--- a/Result/checksun_type/電阻器材料(氧化鋁陶瓷基板、導電漿墨).xlsx
+++ b/Result/checksun_type/電阻器材料(氧化鋁陶瓷基板、導電漿墨).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>76.6</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>76.74</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>76.73999999999999</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>72.7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>10866.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>22805.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>22805.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>24824.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>35440.92</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>35440.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-3885.075831923583</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>10866</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>10866.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>77.0</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>77.14</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>72.47</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>72.47</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>17378.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>27706.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>27706.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>24765.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>35335.7</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>35335.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-3149.155131571762</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>17378</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>17378.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>77.26</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>77.32</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>72.23</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>72.23</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>15223.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>29440.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>29440.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>24659.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>35124.82</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>35124.82</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-2683.0843049416</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>15223</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>15223.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>76.78</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>77.34</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>71.99</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>77.34</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>71.98999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>45420.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>33913.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>33913.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>24919.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>35385.58</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>35385.58</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1690.551541722016</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>45420</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>45420.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>76.18</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>77.04</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>71.74</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>71.73999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>25142.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>29029.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>29029</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>22596.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>34755.56</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>34755.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-3447.66361063255</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>25142</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>25142.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>75.36</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>76.87</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>71.49</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>76.87</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>71.48999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>35370.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>26843.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>26843</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>22428.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>34604.28</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>34604.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-3662.050008696431</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>35370</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>35370.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>75.2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>76.91</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>71.24</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>71.23999999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>26048.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>21824.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>21824.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>20128.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>34252.9</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>34252.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-4933.385934191385</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>26048</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>26048.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>74.91999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>77.08</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>70.95</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>70.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>37589.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>19878.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>19878.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>19679.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>33981.94</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>33981.94</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-5574.602044391628</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>37589</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>37589.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>75.1</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>76.96</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>70.72</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>70.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>20996.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>15926.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>15926</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>18147.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>34130.62</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>34130.62</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-7528.067843092274</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>20996</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>20996.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>75.72</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>76.7</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>70.42</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>70.42</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>14212.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>16164.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>16164.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>20662.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>33992.8</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>33992.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-8272.052275411334</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>14212</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>14212.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>76.24000000000001</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>76.48</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>70.11</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>70.11</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>10279.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>18013.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>18013.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>25789.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>33780.52</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>33780.52</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-8312.599597459583</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>10279</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>10279.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>26.73</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>27.47</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>25.74</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>25.74</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>37920.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>56173.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>56173.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>103361.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>90993.62</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>90993.62</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-8584.48455587322</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>37920</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>37920.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>27.29</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>27.51</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>25.58</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>25.58</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>54478.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>67939.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>67939.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>121458.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>90400.56</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>90400.56</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-6006.797548369039</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>54478</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>54478.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>27.79</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>27.57</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>25.42</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>25.42</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>50807.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>83919.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>83919.60000000001</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>121179.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>89478.6</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>89478.60000000001</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-3883.930482349882</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>50807</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>50807.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>28.05</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>27.66</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>25.25</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>56589.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>90473.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>90473</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>123589.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>88652.1</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>88652.10000000001</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-319.2300136671693</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>56589</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>56589.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>28.52</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>27.81</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>25.08</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>25.08</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>81073.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>102311.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>102311.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>119010.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>87807.72</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>87807.72</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>4165.100299224825</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>81073</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>81073.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>29.01</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>27.92</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>24.87</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>24.87</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>96749.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>150549.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>150549</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>111928.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>86349.64</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>86349.64</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>7799.247164098211</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>96749</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>96749.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>29.21</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>28.06</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>24.65</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>24.65</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>134380.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>174977.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>174977.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>104149.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>84680.78</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>84680.78</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>11032.76957234241</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>134380</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>134380.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>28.94</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>28.08</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>24.44</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>24.44</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>83574.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>158439.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>158439</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>92883.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>82444.28</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>82444.28</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>11226.16695653618</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>83574</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>83574.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>28.36</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>28.02</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>24.26</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>24.26</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>115782.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>156706.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>156706.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>86541.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>81072.88</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>81072.88</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>16545.01439979386</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>115782</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>115782.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>27.79</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>27.78</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>24.07</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>24.07</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>322260.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>135709.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>135709</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>78419.1</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>79064.8</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>79064.8</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>20101.61737588362</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>322260</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>322260.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>27.13</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>27.36</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>23.87</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>23.87</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>218892.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>73308.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>73308.60000000001</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>47704.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>72796.34</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>72796.34</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>2341.921006873134</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>218892</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>218892.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>293.9</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>314.2</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>313.06</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>314.2</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>313.06</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>215423673.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>178377059.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>178377059.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>203196614.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>342055488.44</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>342055488.44</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-29757059.1646015</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>215423673</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>215423673.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>291.3</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>315.35</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>312.95</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>315.35</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>312.95</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>145369311.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>201601517.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>201601517</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>213574610.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>341401273.88</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>341401273.88</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-33232461.61026913</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>145369311</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>145369311.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>291.4</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>316.75</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>313.05</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>316.75</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>313.05</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>255529988.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>235452704.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>235452704.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>262643830.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>341945859.18</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>341945859.18</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-29504624.11799899</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>255529988</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>255529988.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>294.4</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>318.42</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>313.22</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>318.42</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>313.22</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>148293165.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>208628721.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>208628721.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>273247364.4</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>345426351.54</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>345426351.54</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-34928335.08911312</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>148293165</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>148293165.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>298.2</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>319.8</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>313.4</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>319.8</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>313.4</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>127269159.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>208479663.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>208479663.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>276125257.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>349062466.22</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>349062466.22</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-29939393.47323638</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>127269159</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>127269159.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>301.5</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>320.95</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>313.2</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>320.95</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>313.2</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>331545962.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>228016169.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>228016169.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>310860645.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>348437711.32</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>348437711.32</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-19490497.8979398</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>331545962</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>331545962.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>306.4</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>322.75</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>313.15</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>313.15</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>314625250.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>225547703.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>225547703.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>318140668.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>344419428.18</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>344419428.18</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-25754215.32973254</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>314625250</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>314625250.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>310.2</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>324.27</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>312.96</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>324.27</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>312.96</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>121410071.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>289834955.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>289834955.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>319654840.6</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>340158543.92</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>340158543.92</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-31969656.25623173</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>121410071</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>121410071.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>315.5</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>325.05</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>312.53</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>325.05</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>312.53</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>147547875.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>337866007.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>337866007.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>378484318.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>339527483.9</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>339527483.9</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-19005457.82065082</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>147547875</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>147547875.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>320.4</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>326.12</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>312.18</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>326.12</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>312.18</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>224951691.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>343770852.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>343770852.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>476802600.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>340098445.2</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>340098445.2</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-2606886.990511954</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>224951691</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>224951691.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>325.1</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>326.8</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>311.79</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>326.8</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>311.79</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>319203632.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>393705122.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>393705122</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>465510492.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>339342581.32</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>339342581.32</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>12619479.87363327</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>319203632</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>319203632.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>174.8</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>174.25</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>169.68</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>174.25</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>169.68</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>174920.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>330323.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>330323.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>389597.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>211843.7</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>211843.7</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>10191.75853036175</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>174920</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>174920.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>177.5</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>174.42</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>169.77</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>174.42</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>169.77</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>163410.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>540797.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>540797.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>388405.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>210395.5</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>210395.5</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>27168.1896322539</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>163410</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>163410.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>179.6</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>175.02</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>170.11</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>175.02</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>170.11</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>203938.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>573351.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>573351.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>391089.1</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>209730.88</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>209730.88</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>51683.15586237633</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>203938</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>203938.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>181.2</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>175.6</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>170.27</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>175.6</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>170.27</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>335990.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>559007.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>559007.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>378699.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>207102.88</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>207102.88</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>80516.42348175216</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>335990</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>335990.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>181.6</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>175.75</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>170.28</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>175.75</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>170.28</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>773361.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>525593.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>525593.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>360604.4</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>201294.06</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>201294.06</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>104682.7906707979</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>773361</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>773361.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>181.2</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>175.1</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>170.06</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>175.1</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>170.06</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1227288.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>448871.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>448871.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>294742.4</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>186570.02</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>186570.02</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>88606.32270262047</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1227288</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1227288.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>178.8</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>174.2</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>169.75</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>169.75</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>326179.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>236013.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>236013</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>181083.3</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>163556.08</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>163556.08</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>13840.39265155917</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>326179</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>326179.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>176.4</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>173.75</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>169.66</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>173.75</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>169.66</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>132221.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>208827.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>208827</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>155954.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>158247.22</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>158247.22</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>3085.014269630134</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>132221</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>132221.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>173.4</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>172.7</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>169.57</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>169.57</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>168917.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>198391.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>198391.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>148197.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>158796.84</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>158796.84</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>8391.223214387574</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>168917</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>168917.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>171.8</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>171.9</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>169.65</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>171.9</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>169.65</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>389753.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>195615.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>195615.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>134490.8</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>162120.26</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>162120.26</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>11740.12087781297</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>389753</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>389753.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>170.5</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>170.55</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>169.86</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>170.55</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>169.86</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>162995.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>140613.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>140613.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>106093.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>175583.3</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>175583.3</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-7556.029634358332</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>162995</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>162995.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>41.79</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>43.65</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>47.07</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>47.07</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>18788.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>11702.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>11702.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>11910.8</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>21841.68</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>21841.68</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-835.0067717372658</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>18788</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>18788.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>41.26000000000001</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>47.26</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>47.26</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>10470.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>9823.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>9823.799999999999</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>12026.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>22264.28</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>22264.28</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-1547.487138612682</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>10470</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>10470.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>41.17</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>43.97</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>47.52</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>47.52</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>5468.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>11849.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>11849.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>12661.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>22603.46</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>22603.46</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-1618.834550627105</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>5468</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>5468.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>41.75</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>44.22</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>12727.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>12695.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>12695.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>17521.5</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>23333.98</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>23333.98</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-1127.015333839599</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>12727</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>12727.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>42.59</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>44.56</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>48.12</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>48.12</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>11061.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>11822.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>11822.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>17187.6</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>24177.16</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>24177.16</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-1161.915905077462</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>11061</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>11061.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>43.29</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>44.84</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>48.39</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>48.39</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>9393.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>12118.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>12118.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>17166.1</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>25730.42</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>25730.42</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-991.7768673787868</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>9393</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>9393.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>44.42</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>45.18</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>48.65</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>48.65</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>20598.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>14229.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>14229</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>17330.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>25955.2</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>25955.2</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-534.58621111715</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>20598</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>20598.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>45.3</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>45.46</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>48.9</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>48.9</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>9697.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>13473.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>13473.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>17029.4</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>26019.26</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>26019.26</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-1062.900051774917</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>9697</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>9697.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>45.48</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>45.64</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>49.1</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>8363.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>22347.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>22347.8</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>17369.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>26332.84</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>26332.84</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-611.7091080083301</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>8363</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>8363.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>45.25</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>45.78</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>49.3</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>49.3</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>12543.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>22552.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>22552.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>18149.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>27319.1</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>27319.1</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>197.6247083728013</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>12543</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>12543.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>45.05</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>45.85</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>49.54</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>49.54</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>19944.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>22213.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>22213.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>18422.7</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>29048.06</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>29048.06</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>898.9007064753896</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>19944</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>19944.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
